--- a/Rproj/stomach_dat.xlsx
+++ b/Rproj/stomach_dat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ainsleylotito/Library/CloudStorage/Dropbox-InsightExposure/Ainsley Lotito/Meta-Analysis/Rproj/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D2A4C8E7-D89E-B144-A230-15060321CB89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98B63781-CCAE-0A49-92DE-E3B8A27406AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1640" yWindow="2500" windowWidth="27640" windowHeight="15140" xr2:uid="{4AE84EFA-2284-6A4F-B200-A8FD21DAB342}"/>
   </bookViews>

--- a/Rproj/stomach_dat.xlsx
+++ b/Rproj/stomach_dat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ainsleylotito/Library/CloudStorage/Dropbox-InsightExposure/Ainsley Lotito/Meta-Analysis/Rproj/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98B63781-CCAE-0A49-92DE-E3B8A27406AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{937D1C5D-C23D-2A49-B656-EB58C9D06693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1640" yWindow="2500" windowWidth="27640" windowHeight="15140" xr2:uid="{4AE84EFA-2284-6A4F-B200-A8FD21DAB342}"/>
+    <workbookView xWindow="1460" yWindow="1840" windowWidth="27640" windowHeight="15140" activeTab="1" xr2:uid="{4AE84EFA-2284-6A4F-B200-A8FD21DAB342}"/>
   </bookViews>
   <sheets>
     <sheet name="Stomach_Cancers" sheetId="1" r:id="rId1"/>
